--- a/bof-web/public/data/driver_templates_expanded.xlsx
+++ b/bof-web/public/data/driver_templates_expanded.xlsx
@@ -397,70 +397,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Driver_ID</v>
       </c>
       <c r="B1" t="str">
+        <v>CDL_Number</v>
+      </c>
+      <c r="C1" t="str">
         <v>Medical_Issue_Date</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Medical_Expiration_Date</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Examiner_Name</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>5875_Vision_Result</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>5875_Hearing_Result</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>5875_Blood_Pressure</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>MCSA_Examiner_License</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>MCSA_Registry_Number</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>MCSA_Examiner_Telephone</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Driver_License_State</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Driver_License_Number</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Driver_Signature_Date</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>App_Submission_Date</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>App_Status</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Safety_Ack_Date</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Safety_Ack_Status</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Incident_Report_Count</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>Last_Incident_Date</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>Qual_File_Status</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>BOF_Medical_Summary_Status</v>
       </c>
     </row>
@@ -469,63 +472,66 @@
         <v>DRV-001</v>
       </c>
       <c r="B2" t="str">
-        <v>2024-01-15</v>
+        <v>OH1668243</v>
       </c>
       <c r="C2" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D2" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>Dr. Jordan Ellis, MD</v>
       </c>
-      <c r="E2" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F2" t="str">
         <v>Pass</v>
       </c>
       <c r="G2" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H2" t="str">
         <v>128/82</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>4321</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>OH</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>OH441134921</v>
       </c>
-      <c r="M2" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N2" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O2" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>Complete</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R2" t="str">
+      <c r="S2" t="str">
         <v>1</v>
       </c>
-      <c r="S2" t="str">
+      <c r="T2" t="str">
         <v/>
       </c>
-      <c r="T2" t="str">
+      <c r="U2" t="str">
         <v>Current</v>
       </c>
-      <c r="U2" t="str">
+      <c r="V2" t="str">
         <v>Pending review</v>
       </c>
     </row>
@@ -534,63 +540,66 @@
         <v>DRV-002</v>
       </c>
       <c r="B3" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00002</v>
       </c>
       <c r="C3" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D3" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Demo Examiner 2</v>
       </c>
-      <c r="E3" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F3" t="str">
         <v>Pass</v>
       </c>
       <c r="G3" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H3" t="str">
         <v>128/82</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>4321</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>OH</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>DL-0002</v>
       </c>
-      <c r="M3" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N3" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O3" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>Complete</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R3" t="str">
+      <c r="S3" t="str">
         <v>2</v>
       </c>
-      <c r="S3" t="str">
+      <c r="T3" t="str">
         <v/>
       </c>
-      <c r="T3" t="str">
+      <c r="U3" t="str">
         <v>Current</v>
       </c>
-      <c r="U3" t="str">
+      <c r="V3" t="str">
         <v>Reviewed</v>
       </c>
     </row>
@@ -599,63 +608,66 @@
         <v>DRV-003</v>
       </c>
       <c r="B4" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00003</v>
       </c>
       <c r="C4" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D4" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>Demo Examiner 3</v>
       </c>
-      <c r="E4" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F4" t="str">
         <v>Pass</v>
       </c>
       <c r="G4" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H4" t="str">
         <v>128/82</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>4321</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>OH</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>DL-0003</v>
       </c>
-      <c r="M4" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N4" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O4" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>Complete</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="R4" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R4" t="str">
+      <c r="S4" t="str">
         <v>0</v>
       </c>
-      <c r="S4" t="str">
+      <c r="T4" t="str">
         <v>2025-11-01</v>
       </c>
-      <c r="T4" t="str">
+      <c r="U4" t="str">
         <v>Current</v>
       </c>
-      <c r="U4" t="str">
+      <c r="V4" t="str">
         <v>Pending review</v>
       </c>
     </row>
@@ -664,63 +676,66 @@
         <v>DRV-004</v>
       </c>
       <c r="B5" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00004</v>
       </c>
       <c r="C5" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D5" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>Demo Examiner 4</v>
       </c>
-      <c r="E5" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F5" t="str">
         <v>Pass</v>
       </c>
       <c r="G5" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H5" t="str">
         <v>128/82</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>4321</v>
       </c>
-      <c r="J5" t="str">
+      <c r="K5" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
         <v>OH</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <v>DL-0004</v>
       </c>
-      <c r="M5" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N5" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O5" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>Complete</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="R5" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R5" t="str">
+      <c r="S5" t="str">
         <v>1</v>
       </c>
-      <c r="S5" t="str">
+      <c r="T5" t="str">
         <v/>
       </c>
-      <c r="T5" t="str">
+      <c r="U5" t="str">
         <v>Current</v>
       </c>
-      <c r="U5" t="str">
+      <c r="V5" t="str">
         <v>Reviewed</v>
       </c>
     </row>
@@ -729,63 +744,66 @@
         <v>DRV-005</v>
       </c>
       <c r="B6" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00005</v>
       </c>
       <c r="C6" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D6" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>Demo Examiner 5</v>
       </c>
-      <c r="E6" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F6" t="str">
         <v>Pass</v>
       </c>
       <c r="G6" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H6" t="str">
         <v>128/82</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>4321</v>
       </c>
-      <c r="J6" t="str">
+      <c r="K6" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <v>OH</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <v>DL-0005</v>
       </c>
-      <c r="M6" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N6" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O6" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>Complete</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="R6" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R6" t="str">
+      <c r="S6" t="str">
         <v>2</v>
       </c>
-      <c r="S6" t="str">
+      <c r="T6" t="str">
         <v/>
       </c>
-      <c r="T6" t="str">
+      <c r="U6" t="str">
         <v>Current</v>
       </c>
-      <c r="U6" t="str">
+      <c r="V6" t="str">
         <v>Pending review</v>
       </c>
     </row>
@@ -794,63 +812,66 @@
         <v>DRV-006</v>
       </c>
       <c r="B7" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00006</v>
       </c>
       <c r="C7" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D7" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>Demo Examiner 6</v>
       </c>
-      <c r="E7" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F7" t="str">
         <v>Pass</v>
       </c>
       <c r="G7" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H7" t="str">
         <v>128/82</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>4321</v>
       </c>
-      <c r="J7" t="str">
+      <c r="K7" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
         <v>OH</v>
       </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
         <v>DL-0006</v>
       </c>
-      <c r="M7" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N7" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O7" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <v>Complete</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="R7" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R7" t="str">
+      <c r="S7" t="str">
         <v>0</v>
       </c>
-      <c r="S7" t="str">
+      <c r="T7" t="str">
         <v>2025-11-01</v>
       </c>
-      <c r="T7" t="str">
+      <c r="U7" t="str">
         <v>Current</v>
       </c>
-      <c r="U7" t="str">
+      <c r="V7" t="str">
         <v>Reviewed</v>
       </c>
     </row>
@@ -859,63 +880,66 @@
         <v>DRV-007</v>
       </c>
       <c r="B8" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00007</v>
       </c>
       <c r="C8" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D8" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D8" t="str">
+      <c r="E8" t="str">
         <v>Demo Examiner 7</v>
       </c>
-      <c r="E8" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F8" t="str">
         <v>Pass</v>
       </c>
       <c r="G8" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H8" t="str">
         <v>128/82</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
         <v>4321</v>
       </c>
-      <c r="J8" t="str">
+      <c r="K8" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
         <v>OH</v>
       </c>
-      <c r="L8" t="str">
+      <c r="M8" t="str">
         <v>DL-0007</v>
       </c>
-      <c r="M8" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N8" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O8" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>Complete</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Q8" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="R8" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R8" t="str">
+      <c r="S8" t="str">
         <v>1</v>
       </c>
-      <c r="S8" t="str">
+      <c r="T8" t="str">
         <v/>
       </c>
-      <c r="T8" t="str">
+      <c r="U8" t="str">
         <v>Current</v>
       </c>
-      <c r="U8" t="str">
+      <c r="V8" t="str">
         <v>Pending review</v>
       </c>
     </row>
@@ -924,63 +948,66 @@
         <v>DRV-008</v>
       </c>
       <c r="B9" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00008</v>
       </c>
       <c r="C9" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D9" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D9" t="str">
+      <c r="E9" t="str">
         <v>Demo Examiner 8</v>
       </c>
-      <c r="E9" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F9" t="str">
         <v>Pass</v>
       </c>
       <c r="G9" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H9" t="str">
         <v>128/82</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>4321</v>
       </c>
-      <c r="J9" t="str">
+      <c r="K9" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
         <v>OH</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <v>DL-0008</v>
       </c>
-      <c r="M9" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N9" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O9" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
         <v>Complete</v>
       </c>
-      <c r="P9" t="str">
+      <c r="Q9" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="R9" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R9" t="str">
+      <c r="S9" t="str">
         <v>2</v>
       </c>
-      <c r="S9" t="str">
+      <c r="T9" t="str">
         <v/>
       </c>
-      <c r="T9" t="str">
+      <c r="U9" t="str">
         <v>Current</v>
       </c>
-      <c r="U9" t="str">
+      <c r="V9" t="str">
         <v>Reviewed</v>
       </c>
     </row>
@@ -989,63 +1016,66 @@
         <v>DRV-009</v>
       </c>
       <c r="B10" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00009</v>
       </c>
       <c r="C10" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D10" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D10" t="str">
+      <c r="E10" t="str">
         <v>Demo Examiner 9</v>
       </c>
-      <c r="E10" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F10" t="str">
         <v>Pass</v>
       </c>
       <c r="G10" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H10" t="str">
         <v>128/82</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
         <v>4321</v>
       </c>
-      <c r="J10" t="str">
+      <c r="K10" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K10" t="str">
+      <c r="L10" t="str">
         <v>OH</v>
       </c>
-      <c r="L10" t="str">
+      <c r="M10" t="str">
         <v>DL-0009</v>
       </c>
-      <c r="M10" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N10" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O10" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
         <v>Complete</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Q10" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="R10" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R10" t="str">
+      <c r="S10" t="str">
         <v>0</v>
       </c>
-      <c r="S10" t="str">
+      <c r="T10" t="str">
         <v>2025-11-01</v>
       </c>
-      <c r="T10" t="str">
+      <c r="U10" t="str">
         <v>Current</v>
       </c>
-      <c r="U10" t="str">
+      <c r="V10" t="str">
         <v>Pending review</v>
       </c>
     </row>
@@ -1054,63 +1084,66 @@
         <v>DRV-010</v>
       </c>
       <c r="B11" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00010</v>
       </c>
       <c r="C11" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D11" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D11" t="str">
+      <c r="E11" t="str">
         <v>Demo Examiner 10</v>
       </c>
-      <c r="E11" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F11" t="str">
         <v>Pass</v>
       </c>
       <c r="G11" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H11" t="str">
         <v>128/82</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>4321</v>
       </c>
-      <c r="J11" t="str">
+      <c r="K11" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K11" t="str">
+      <c r="L11" t="str">
         <v>OH</v>
       </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
         <v>DL-0010</v>
       </c>
-      <c r="M11" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N11" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O11" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <v>Complete</v>
       </c>
-      <c r="P11" t="str">
+      <c r="Q11" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="R11" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R11" t="str">
+      <c r="S11" t="str">
         <v>1</v>
       </c>
-      <c r="S11" t="str">
+      <c r="T11" t="str">
         <v/>
       </c>
-      <c r="T11" t="str">
+      <c r="U11" t="str">
         <v>Current</v>
       </c>
-      <c r="U11" t="str">
+      <c r="V11" t="str">
         <v>Reviewed</v>
       </c>
     </row>
@@ -1119,63 +1152,66 @@
         <v>DRV-011</v>
       </c>
       <c r="B12" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00011</v>
       </c>
       <c r="C12" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D12" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D12" t="str">
+      <c r="E12" t="str">
         <v>Demo Examiner 11</v>
       </c>
-      <c r="E12" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F12" t="str">
         <v>Pass</v>
       </c>
       <c r="G12" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H12" t="str">
         <v>128/82</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <v>4321</v>
       </c>
-      <c r="J12" t="str">
+      <c r="K12" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K12" t="str">
+      <c r="L12" t="str">
         <v>OH</v>
       </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
         <v>DL-0011</v>
       </c>
-      <c r="M12" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N12" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O12" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <v>Complete</v>
       </c>
-      <c r="P12" t="str">
+      <c r="Q12" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="R12" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R12" t="str">
+      <c r="S12" t="str">
         <v>2</v>
       </c>
-      <c r="S12" t="str">
+      <c r="T12" t="str">
         <v/>
       </c>
-      <c r="T12" t="str">
+      <c r="U12" t="str">
         <v>Current</v>
       </c>
-      <c r="U12" t="str">
+      <c r="V12" t="str">
         <v>Pending review</v>
       </c>
     </row>
@@ -1184,69 +1220,72 @@
         <v>DRV-012</v>
       </c>
       <c r="B13" t="str">
-        <v>2024-01-15</v>
+        <v>DLN-00012</v>
       </c>
       <c r="C13" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="D13" t="str">
         <v>2026-04-22</v>
       </c>
-      <c r="D13" t="str">
+      <c r="E13" t="str">
         <v>Demo Examiner 12</v>
       </c>
-      <c r="E13" t="str">
-        <v>Pass</v>
-      </c>
       <c r="F13" t="str">
         <v>Pass</v>
       </c>
       <c r="G13" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H13" t="str">
         <v>128/82</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>ME-441300</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>4321</v>
       </c>
-      <c r="J13" t="str">
+      <c r="K13" t="str">
         <v>440-555-0100</v>
       </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <v>OH</v>
       </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
         <v>DL-0012</v>
       </c>
-      <c r="M13" t="str">
-        <v>2024-01-15</v>
-      </c>
       <c r="N13" t="str">
+        <v>2024-01-15</v>
+      </c>
+      <c r="O13" t="str">
         <v>2024-02-01</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <v>Complete</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Q13" t="str">
         <v>2024-02-10</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="R13" t="str">
         <v>Acknowledged</v>
       </c>
-      <c r="R13" t="str">
+      <c r="S13" t="str">
         <v>0</v>
       </c>
-      <c r="S13" t="str">
+      <c r="T13" t="str">
         <v>2025-11-01</v>
       </c>
-      <c r="T13" t="str">
+      <c r="U13" t="str">
         <v>Current</v>
       </c>
-      <c r="U13" t="str">
+      <c r="V13" t="str">
         <v>Reviewed</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V13"/>
   </ignoredErrors>
 </worksheet>
 </file>